--- a/data/exports/毛毛矩阵/dist_order_2026-10-14.xlsx
+++ b/data/exports/毛毛矩阵/dist_order_2026-10-14.xlsx
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>殷桃小丸子🍒🍒</t>
+          <t>好事花生🥜</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
